--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6271-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6271-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63294C13-DE0F-461F-A342-BA40AC2E311B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{058169E7-BA8D-4F3F-B3CF-30C0F57C5819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FBDB2865-6103-478C-97AF-7942FD1C4DC9}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{FD51B335-4965-4ACE-8798-3D5FE6B87E05}"/>
   </bookViews>
   <sheets>
     <sheet name="6271-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1549,23 +1549,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D0B7D2-88C1-408C-BBCC-3509DFF3D0F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8433DD84-1739-4264-BDEC-8550DD1E5333}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="6" width="7.77734375" customWidth="1"/>
-    <col min="7" max="9" width="7.44140625" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="Q1" s="35"/>
       <c r="R1" s="27"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
@@ -1623,7 +1623,7 @@
       <c r="Q2" s="37"/>
       <c r="R2" s="38"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="30"/>
       <c r="B4" s="31"/>
       <c r="C4" s="7"/>
@@ -1719,7 +1719,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="42">
         <v>2026</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="44"/>
       <c r="B6" s="45"/>
       <c r="C6" s="47"/>
@@ -1799,7 +1799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="52">
         <v>2025</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="54">
         <v>2024</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
         <v>2023</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
         <v>26</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="24" t="s">
         <v>39</v>
@@ -2487,7 +2487,7 @@
       <c r="Q19" s="61"/>
       <c r="R19" s="61"/>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="54">
         <v>2022</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="52">
         <v>2021</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="54">
         <v>2020</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="52">
         <v>2019</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="54">
         <v>2018</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="52">
         <v>2017</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="54">
         <v>2016</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="52">
         <v>2015</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="54">
         <v>2014</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="52">
         <v>2013</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="54">
         <v>2012</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="52">
         <v>2011</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="54">
         <v>2010</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="52">
         <v>2009</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="54">
         <v>2008</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="52">
         <v>2007</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="54">
         <v>2006</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="52">
         <v>2005</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="54">
         <v>2004</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="52">
         <v>2003</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="54">
         <v>2002</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="52">
         <v>2001</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="54">
         <v>2000</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="52" t="s">
         <v>40</v>
       </c>
